--- a/data/Feature_Meaning.xlsx
+++ b/data/Feature_Meaning.xlsx
@@ -1,40 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ian32\Downloads\final\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B66366-0EE0-479F-A9E8-8C00780A465A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EB7DEF-C809-4DDD-85C7-001B1C995598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD47F78A-EF2B-4774-810B-9E2FBB19141E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="76">
   <si>
     <t>Feature</t>
   </si>
@@ -123,40 +114,196 @@
     <t>The city of the audience.</t>
   </si>
   <si>
+    <t>The id for this bid request.</t>
+  </si>
+  <si>
+    <t>The column describes if the ad slot is above the fold (FirstView) or not (SecondView to TenthView), or unknown (Na).</t>
+  </si>
+  <si>
+    <t>The URL of the hosting web page of the ad slot. The values were hashed.</t>
+  </si>
+  <si>
+    <t>The ad exchange id.</t>
+  </si>
+  <si>
+    <t>The column describes the device, operation system,  and browser of the user.</t>
+  </si>
+  <si>
+    <t>Floor (or reserve) price of the ad slot. No bid lower than the floor price could win auctions.</t>
+  </si>
+  <si>
+    <t>The IP address of the audience.</t>
+  </si>
+  <si>
+    <t>The ad material ID (image, video, HTML5, etc.) that is delivered to the user.</t>
+  </si>
+  <si>
+    <t>Meaning</t>
+  </si>
+  <si>
+    <t>A list of user tags , segmented by commas, in proprietary audience database. Only a part of  the user tags are released in this dataset.</t>
+  </si>
+  <si>
+    <t>The region of the audience.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完全無用的，都是空值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>trqRTJkrBoq7JsNr5SqfNX</t>
+  </si>
+  <si>
+    <t>0/1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>115.45.195.*</t>
+  </si>
+  <si>
+    <t>false true</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>The offered bid price for this bid request.</t>
-  </si>
-  <si>
-    <t>The id for this bid request.</t>
-  </si>
-  <si>
-    <t>The column describes if the ad slot is above the fold (FirstView) or not (SecondView to TenthView), or unknown (Na).</t>
-  </si>
-  <si>
-    <t>The URL of the hosting web page of the ad slot. The values were hashed.</t>
-  </si>
-  <si>
-    <t>The ad exchange id.</t>
-  </si>
-  <si>
-    <t>The column describes the device, operation system,  and browser of the user.</t>
-  </si>
-  <si>
-    <t>Floor (or reserve) price of the ad slot. No bid lower than the floor price could win auctions.</t>
-  </si>
-  <si>
-    <t>The IP address of the audience.</t>
-  </si>
-  <si>
-    <t>The ad material ID (image, video, HTML5, etc.) that is delivered to the user.</t>
-  </si>
-  <si>
-    <t>Meaning</t>
-  </si>
-  <si>
-    <t>A list of user tags , segmented by commas, in proprietary audience database. Only a part of  the user tags are released in this dataset.</t>
-  </si>
-  <si>
-    <t>The region of the audience.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-399</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>要預測的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10074,10083,13800,10077,10006,10063,10075,10048,10031,10059,10076,10024,10079,10057,10111</t>
+  </si>
+  <si>
+    <t>160-1000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要再分析8種廣告出現的頻率與click關係</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>長得很奇特，但其實只有八種</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2013-06-06 00:01:04.828000+00:00</t>
+  </si>
+  <si>
+    <t>都是300</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>都不一樣，沒什麼用處</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要生出一個新特徵 面積</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>f41292b3547399af082eccc2ad28f23c</t>
+  </si>
+  <si>
+    <t>0.1.2.255</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-395</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>60-600</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要拆解</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-300</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要拆解開來</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要拆解，年、月、日、時間</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mm_34022157_3445226_11175096</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mm時的creative_id
+77819d3e0b3467fe5c7b16d68ad923a1
+55%
+48f2e9ba15708c0146bda5e1dd653caa
+23%
+cb7c76e7784031272e37af8e7e9b062c
+22%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>以0為主</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0-20之間比較多</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>60-80之間比較多</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>950-1000比較多</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">有三個比較常出現
+832b91d59d0cb573143165
+a499988a822facd86dd0e8
+48f2e9ba15708c0146bda5e
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>90-120為主</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>以3為主</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>News_F_Width1
+23%
+Ent_F_Width1
+23%
+mm_10027070_118039_9659846
+10%
+其他
+44%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>從domain前三名click true觀察到的有趣現象
+5F1RQS9rg5scFsf
+31xSTvprdN1RFt
+5F97t5E0BTK7XhNrUMpEN</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -188,12 +335,48 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -208,9 +391,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -229,9 +422,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -269,7 +462,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -375,7 +568,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -517,7 +710,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -525,180 +718,301 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E2319B-3F37-4D7E-830B-7B2BC9D9A0DE}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="109.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="109.875" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="60" x14ac:dyDescent="0.3">
+      <c r="C1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="12" spans="1:5" ht="75" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="120" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>22</v>
       </c>
+    </row>
+    <row r="24" spans="1:5" ht="105" x14ac:dyDescent="0.3">
+      <c r="B24" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/data/Feature_Meaning.xlsx
+++ b/data/Feature_Meaning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ian32\Downloads\final\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EB7DEF-C809-4DDD-85C7-001B1C995598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DECF63E6-E7AE-4FCC-A9C8-73C5E2D82525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD47F78A-EF2B-4774-810B-9E2FBB19141E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="89">
   <si>
     <t>Feature</t>
   </si>
@@ -304,6 +304,63 @@
 5F1RQS9rg5scFsf
 31xSTvprdN1RFt
 5F97t5E0BTK7XhNrUMpEN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以直接進行 Embedding 的「標準類別特徵」</t>
+  </si>
+  <si>
+    <t>類別特徵包含0和1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>要預測的項目，預測 click (點擊率)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ad_slot_size</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>「多熱點徵 (Multi-Hot)」的特殊 Embedding 方式
+特徵列表:
+user_tags
+Embedding 處理流程 (三步驟)：
+建立詞典與編碼：建立一個包含所有不重複tag的詞彙表，並將每個 tag 對應到一個整數索引。將每筆資料的 user_tags（例如 ['1001', '1005']）轉換為一個整數索引列表（例如 [5, 18]）。
+共享嵌入層：在模型中，為所有的 tag 建立一個共享的 (shared) Embedding 層。
+池化操作 (Pooling)：對於一個用戶的索引列表 [5, 18]，模型會先查詢到索引 5 和 18 各自的嵌入向量，然後用一個池化層（最常用的是 AveragePooling）將這幾個向量聚合成一個單一的向量。這個聚合後的向量代表了該用戶的綜合興趣。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有八種類別，類別特徵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>timestamp 提取出 hour, day_of_week的特徵，進行 Embedding：對每一個新特徵，都遵循第一類的處理流程：標籤編碼 -&gt; 建立獨立的嵌入層。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有四種類別，類別特徵，0.1.2.255</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有三種類別，類別特徵，1.2.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新加入的特徵，由ad_slot_width 和 ad_slot_height相乘</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>參考C:\Users\ian32\Downloads\final\feature_test.ipynb</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>參考C:\Users\ian32\Downloads\final\feature_test02.ipynb</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>符合deepfm處理方式</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -391,18 +448,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -718,301 +776,377 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E2319B-3F37-4D7E-830B-7B2BC9D9A0DE}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="109.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="109.875" customWidth="1"/>
-    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="101.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="109.875" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="60" x14ac:dyDescent="0.3">
-      <c r="C1" s="9" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="75" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
+      <c r="C16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
+      <c r="E17" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C18" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C19" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="4" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C22" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="120" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="9" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="105" x14ac:dyDescent="0.3">
-      <c r="B24" s="9" t="s">
+      <c r="E23" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C24" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="9"/>
+      <c r="D24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>85</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
